--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/125.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/125.xlsx
@@ -426,13 +426,13 @@
         <v>-20.57290793280004</v>
       </c>
       <c r="E2">
-        <v>-3.891528101303093</v>
+        <v>-4.011310767279982</v>
       </c>
       <c r="F2">
-        <v>-2.464157570068887</v>
+        <v>-3.293072413621725</v>
       </c>
       <c r="G2">
-        <v>-7.043829031302403</v>
+        <v>-6.913539201058846</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.0865542496315</v>
       </c>
       <c r="E3">
-        <v>-4.331165943389754</v>
+        <v>-6.080135060736169</v>
       </c>
       <c r="F3">
-        <v>-2.341474207623455</v>
+        <v>-3.193071679150174</v>
       </c>
       <c r="G3">
-        <v>-6.398352104237464</v>
+        <v>-6.742877267963877</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.6082980206005</v>
       </c>
       <c r="E4">
-        <v>-6.000071640280557</v>
+        <v>-3.925867519703257</v>
       </c>
       <c r="F4">
-        <v>-2.031552462207448</v>
+        <v>-2.92654981064087</v>
       </c>
       <c r="G4">
-        <v>-5.970056896185333</v>
+        <v>-6.749021640484765</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.16835643671277</v>
       </c>
       <c r="E5">
-        <v>-5.024475313964086</v>
+        <v>-5.802634702020137</v>
       </c>
       <c r="F5">
-        <v>-2.227934371280813</v>
+        <v>-2.945241499707844</v>
       </c>
       <c r="G5">
-        <v>-6.501677541063657</v>
+        <v>-7.030583538599779</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.7235896232085</v>
       </c>
       <c r="E6">
-        <v>-6.121434743686122</v>
+        <v>-6.296116100057999</v>
       </c>
       <c r="F6">
-        <v>-1.660409397218298</v>
+        <v>-2.741396376507971</v>
       </c>
       <c r="G6">
-        <v>-6.382411827465873</v>
+        <v>-6.812395413743033</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.240299707073</v>
       </c>
       <c r="E7">
-        <v>-7.709806058824516</v>
+        <v>-7.861097846946775</v>
       </c>
       <c r="F7">
-        <v>-1.563479468516784</v>
+        <v>-2.450469599841744</v>
       </c>
       <c r="G7">
-        <v>-6.578468955392592</v>
+        <v>-6.086415950799636</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.69330972125515</v>
       </c>
       <c r="E8">
-        <v>-7.954488566406961</v>
+        <v>-9.103443934685069</v>
       </c>
       <c r="F8">
-        <v>-1.653607380311485</v>
+        <v>-2.523996314377851</v>
       </c>
       <c r="G8">
-        <v>-5.968779025607174</v>
+        <v>-6.036112211330411</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.07613668731348</v>
       </c>
       <c r="E9">
-        <v>-8.985341332565026</v>
+        <v>-8.269203924518028</v>
       </c>
       <c r="F9">
-        <v>-1.520668730210625</v>
+        <v>-1.91391320310269</v>
       </c>
       <c r="G9">
-        <v>-5.203443797292922</v>
+        <v>-6.604976493525536</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.37861332958457</v>
       </c>
       <c r="E10">
-        <v>-9.708285037045552</v>
+        <v>-10.09856704092261</v>
       </c>
       <c r="F10">
-        <v>-1.371856595719315</v>
+        <v>-2.046111470688083</v>
       </c>
       <c r="G10">
-        <v>-5.328519518312127</v>
+        <v>-4.819135807821087</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.62157875696146</v>
       </c>
       <c r="E11">
-        <v>-10.40290766508211</v>
+        <v>-10.45613987704227</v>
       </c>
       <c r="F11">
-        <v>-1.426137324118044</v>
+        <v>-2.140558148514187</v>
       </c>
       <c r="G11">
-        <v>-4.288819517885235</v>
+        <v>-5.714919772564781</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.83712254044356</v>
       </c>
       <c r="E12">
-        <v>-10.94636530226862</v>
+        <v>-10.30670929173717</v>
       </c>
       <c r="F12">
-        <v>-1.180614604194509</v>
+        <v>-1.885377989918302</v>
       </c>
       <c r="G12">
-        <v>-3.372970336628018</v>
+        <v>-5.046368343091122</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.05715793678963</v>
       </c>
       <c r="E13">
-        <v>-11.62726212558793</v>
+        <v>-10.88592375968824</v>
       </c>
       <c r="F13">
-        <v>-1.253933061402736</v>
+        <v>-1.679858097712852</v>
       </c>
       <c r="G13">
-        <v>-3.416222614098597</v>
+        <v>-5.213901810651479</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.33469223646366</v>
       </c>
       <c r="E14">
-        <v>-12.54784654965922</v>
+        <v>-12.84499595709453</v>
       </c>
       <c r="F14">
-        <v>-1.084033090794392</v>
+        <v>-1.303035863310936</v>
       </c>
       <c r="G14">
-        <v>-2.663474079924653</v>
+        <v>-3.732177769821099</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.72045343909447</v>
       </c>
       <c r="E15">
-        <v>-13.06419221296181</v>
+        <v>-13.00553488914045</v>
       </c>
       <c r="F15">
-        <v>-1.346876802315089</v>
+        <v>-1.398353579390532</v>
       </c>
       <c r="G15">
-        <v>-2.53820965780971</v>
+        <v>-3.045941406076654</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.23932411053608</v>
       </c>
       <c r="E16">
-        <v>-13.40930268861236</v>
+        <v>-14.1178503742225</v>
       </c>
       <c r="F16">
-        <v>-0.6451763038317555</v>
+        <v>-1.46152127353375</v>
       </c>
       <c r="G16">
-        <v>-1.232282206205709</v>
+        <v>-3.587175875201021</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.90231226541591</v>
       </c>
       <c r="E17">
-        <v>-14.69475532042967</v>
+        <v>-14.36981466800928</v>
       </c>
       <c r="F17">
-        <v>-0.7288949577866732</v>
+        <v>-0.9898128829141954</v>
       </c>
       <c r="G17">
-        <v>-0.8595842999400977</v>
+        <v>-2.195343077398472</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.69572941116233</v>
       </c>
       <c r="E18">
-        <v>-15.50116332934557</v>
+        <v>-15.19349880526444</v>
       </c>
       <c r="F18">
-        <v>-0.5242635245997845</v>
+        <v>-0.9348765002664742</v>
       </c>
       <c r="G18">
-        <v>-0.4087674505843045</v>
+        <v>-1.808363477676445</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.57898948697866</v>
       </c>
       <c r="E19">
-        <v>-16.66982661650506</v>
+        <v>-16.02045250075314</v>
       </c>
       <c r="F19">
-        <v>-0.2946079542430372</v>
+        <v>-0.5816689047696759</v>
       </c>
       <c r="G19">
-        <v>0.5434182785119529</v>
+        <v>-0.09710276188069709</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.51169523661269</v>
       </c>
       <c r="E20">
-        <v>-17.76023334433799</v>
+        <v>-17.99444149154069</v>
       </c>
       <c r="F20">
-        <v>-0.335365417829829</v>
+        <v>-0.08030245347168655</v>
       </c>
       <c r="G20">
-        <v>0.4553379038941037</v>
+        <v>-0.5688422590446842</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.45635295761121</v>
       </c>
       <c r="E21">
-        <v>-18.15756165377099</v>
+        <v>-17.84559507938258</v>
       </c>
       <c r="F21">
-        <v>-0.2254340554155152</v>
+        <v>-0.03599669678135257</v>
       </c>
       <c r="G21">
-        <v>1.28447396584119</v>
+        <v>-0.3221768214591273</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.37596640877984</v>
       </c>
       <c r="E22">
-        <v>-18.54553866437815</v>
+        <v>-19.18951031063891</v>
       </c>
       <c r="F22">
-        <v>0.160975934598471</v>
+        <v>0.3723777105738633</v>
       </c>
       <c r="G22">
-        <v>0.6289031854270135</v>
+        <v>0.1481424516685124</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.25332360315421</v>
       </c>
       <c r="E23">
-        <v>-18.35005802688904</v>
+        <v>-18.30196110445358</v>
       </c>
       <c r="F23">
-        <v>0.6781509383443769</v>
+        <v>-0.05661417224150102</v>
       </c>
       <c r="G23">
-        <v>1.68502018118315</v>
+        <v>-0.7524384935615857</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.08499626343706</v>
       </c>
       <c r="E24">
-        <v>-18.52635152000765</v>
+        <v>-18.77211633287792</v>
       </c>
       <c r="F24">
-        <v>0.3226810189473735</v>
+        <v>0.2009217489036002</v>
       </c>
       <c r="G24">
-        <v>1.067659717383242</v>
+        <v>0.5669661889327888</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.87449223422089</v>
       </c>
       <c r="E25">
-        <v>-19.41564418868594</v>
+        <v>-19.66100143889552</v>
       </c>
       <c r="F25">
-        <v>0.5695229658984698</v>
+        <v>0.2029496843283204</v>
       </c>
       <c r="G25">
-        <v>1.228913080055602</v>
+        <v>0.2106091354490205</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.63584872001123</v>
       </c>
       <c r="E26">
-        <v>-19.65155051364152</v>
+        <v>-19.42091080395686</v>
       </c>
       <c r="F26">
-        <v>0.05296323190071207</v>
+        <v>0.200436343040518</v>
       </c>
       <c r="G26">
-        <v>1.504201494373697</v>
+        <v>0.351784039425701</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.3888068930906</v>
       </c>
       <c r="E27">
-        <v>-20.28154728911461</v>
+        <v>-20.08935432375507</v>
       </c>
       <c r="F27">
-        <v>0.3123410030254694</v>
+        <v>0.07762865968072374</v>
       </c>
       <c r="G27">
-        <v>1.240592684718151</v>
+        <v>-0.5249378041028697</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.15186152621146</v>
       </c>
       <c r="E28">
-        <v>-19.56604839590269</v>
+        <v>-20.68366672404772</v>
       </c>
       <c r="F28">
-        <v>0.5000291584760291</v>
+        <v>0.3442479261038279</v>
       </c>
       <c r="G28">
-        <v>0.6559139264819271</v>
+        <v>-0.2307362431189178</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.942187474347309</v>
       </c>
       <c r="E29">
-        <v>-20.21336658445512</v>
+        <v>-19.97417711584398</v>
       </c>
       <c r="F29">
-        <v>0.5037484918184386</v>
+        <v>0.3069785747957914</v>
       </c>
       <c r="G29">
-        <v>1.021725898025854</v>
+        <v>-0.2166498718493189</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.777268775459017</v>
       </c>
       <c r="E30">
-        <v>-19.8446582307506</v>
+        <v>-18.96228507035604</v>
       </c>
       <c r="F30">
-        <v>0.4822385980749401</v>
+        <v>0.2124471687032107</v>
       </c>
       <c r="G30">
-        <v>0.4046170356869299</v>
+        <v>-0.693649825875208</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.66931487952608</v>
       </c>
       <c r="E31">
-        <v>-19.86013655490882</v>
+        <v>-19.82697453975065</v>
       </c>
       <c r="F31">
-        <v>0.3132904347217753</v>
+        <v>-0.03373912399889364</v>
       </c>
       <c r="G31">
-        <v>0.55269773765853</v>
+        <v>-1.143268257745785</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.620431677361417</v>
       </c>
       <c r="E32">
-        <v>-18.85365603586004</v>
+        <v>-18.34176186250699</v>
       </c>
       <c r="F32">
-        <v>0.4256551612751618</v>
+        <v>0.2871877938235023</v>
       </c>
       <c r="G32">
-        <v>-0.1664388276551929</v>
+        <v>-0.5306518057036518</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.62747237989038</v>
       </c>
       <c r="E33">
-        <v>-19.51272561446238</v>
+        <v>-18.02077003942129</v>
       </c>
       <c r="F33">
-        <v>0.6483994390169314</v>
+        <v>0.2320209819650846</v>
       </c>
       <c r="G33">
-        <v>-0.3755428155521788</v>
+        <v>-0.08275816805903505</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.681846553615692</v>
       </c>
       <c r="E34">
-        <v>-18.66961432371431</v>
+        <v>-18.40084939135907</v>
       </c>
       <c r="F34">
-        <v>0.6051896068200816</v>
+        <v>0.3073499538329619</v>
       </c>
       <c r="G34">
-        <v>-0.534121257428808</v>
+        <v>-1.007059172078011</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.767432041928828</v>
       </c>
       <c r="E35">
-        <v>-18.13726503326861</v>
+        <v>-18.26183429627161</v>
       </c>
       <c r="F35">
-        <v>0.5649682276856659</v>
+        <v>0.1845462297379563</v>
       </c>
       <c r="G35">
-        <v>-0.8637125502275688</v>
+        <v>-1.80161658586741</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.867131727561969</v>
       </c>
       <c r="E36">
-        <v>-16.6243969652601</v>
+        <v>-17.21370540177428</v>
       </c>
       <c r="F36">
-        <v>0.7745368640639372</v>
+        <v>0.4719278807124715</v>
       </c>
       <c r="G36">
-        <v>-0.957030207888545</v>
+        <v>-1.685462785076541</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.964086993570726</v>
       </c>
       <c r="E37">
-        <v>-16.53048999976305</v>
+        <v>-16.95858929007816</v>
       </c>
       <c r="F37">
-        <v>0.332692415891824</v>
+        <v>0.4182283723847085</v>
       </c>
       <c r="G37">
-        <v>-0.3882056522398911</v>
+        <v>-1.558198793455879</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.03908323991248</v>
       </c>
       <c r="E38">
-        <v>-15.9582584387318</v>
+        <v>-17.34942829625817</v>
       </c>
       <c r="F38">
-        <v>0.7797789306440417</v>
+        <v>0.4512811066928875</v>
       </c>
       <c r="G38">
-        <v>-1.130684874151015</v>
+        <v>-1.649960494713397</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.07938376968426</v>
       </c>
       <c r="E39">
-        <v>-15.69515409888615</v>
+        <v>-16.65880883924439</v>
       </c>
       <c r="F39">
-        <v>0.8108227339984858</v>
+        <v>0.4926815548813478</v>
       </c>
       <c r="G39">
-        <v>-1.433712349542664</v>
+        <v>-2.628935158313437</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.08265284482519</v>
       </c>
       <c r="E40">
-        <v>-16.2178532112215</v>
+        <v>-15.70152113334093</v>
       </c>
       <c r="F40">
-        <v>0.9705473941001312</v>
+        <v>0.6343361304878292</v>
       </c>
       <c r="G40">
-        <v>-1.10790501029529</v>
+        <v>-1.399044316655416</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.0504418136648</v>
       </c>
       <c r="E41">
-        <v>-15.01367763089386</v>
+        <v>-15.97850524602009</v>
       </c>
       <c r="F41">
-        <v>1.156539400515255</v>
+        <v>0.7388464675535937</v>
       </c>
       <c r="G41">
-        <v>-1.212528180972877</v>
+        <v>-2.188245267762274</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.9927155288709</v>
       </c>
       <c r="E42">
-        <v>-14.8005133024048</v>
+        <v>-15.21639476984722</v>
       </c>
       <c r="F42">
-        <v>0.8669809457599685</v>
+        <v>0.4530912825542348</v>
       </c>
       <c r="G42">
-        <v>-1.924997307570508</v>
+        <v>-1.257750233039322</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.92916429543939</v>
       </c>
       <c r="E43">
-        <v>-13.47588484194714</v>
+        <v>-14.60347034138305</v>
       </c>
       <c r="F43">
-        <v>0.7474697462631615</v>
+        <v>0.5219658609637386</v>
       </c>
       <c r="G43">
-        <v>-1.126794983142372</v>
+        <v>-1.890597428871941</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.874811038217326</v>
       </c>
       <c r="E44">
-        <v>-11.83194915073463</v>
+        <v>-13.41821925393346</v>
       </c>
       <c r="F44">
-        <v>1.197582723019784</v>
+        <v>0.163100476084033</v>
       </c>
       <c r="G44">
-        <v>-1.231990878198253</v>
+        <v>-2.460332384543895</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.845076963472364</v>
       </c>
       <c r="E45">
-        <v>-12.28521317111037</v>
+        <v>-12.23491088183317</v>
       </c>
       <c r="F45">
-        <v>1.229014534323511</v>
+        <v>0.4027310181491758</v>
       </c>
       <c r="G45">
-        <v>-0.9013832479189356</v>
+        <v>-1.794293659134542</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.85972214362881</v>
       </c>
       <c r="E46">
-        <v>-12.73441967877524</v>
+        <v>-12.36403126121387</v>
       </c>
       <c r="F46">
-        <v>1.028477772780991</v>
+        <v>0.3548888461496655</v>
       </c>
       <c r="G46">
-        <v>-0.3894702806358927</v>
+        <v>-1.916158150980654</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.926891423466243</v>
       </c>
       <c r="E47">
-        <v>-12.27419992232372</v>
+        <v>-12.63074932331764</v>
       </c>
       <c r="F47">
-        <v>1.253305415654521</v>
+        <v>0.6112187752401596</v>
       </c>
       <c r="G47">
-        <v>-1.363995571031152</v>
+        <v>-2.083943220001996</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.0518921997653</v>
       </c>
       <c r="E48">
-        <v>-10.87565318063885</v>
+        <v>-12.06142504259932</v>
       </c>
       <c r="F48">
-        <v>1.081786897600598</v>
+        <v>0.3681864328686528</v>
       </c>
       <c r="G48">
-        <v>-1.210339910371419</v>
+        <v>-1.881043194445605</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.24314497015686</v>
       </c>
       <c r="E49">
-        <v>-10.120050121615</v>
+        <v>-10.29109964183273</v>
       </c>
       <c r="F49">
-        <v>1.142857765111774</v>
+        <v>0.5954783221466069</v>
       </c>
       <c r="G49">
-        <v>-0.1219053690609168</v>
+        <v>-1.782898761388371</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.49625380770351</v>
       </c>
       <c r="E50">
-        <v>-10.69566898120399</v>
+        <v>-8.848047057600475</v>
       </c>
       <c r="F50">
-        <v>0.9082048107388574</v>
+        <v>0.4070965035050846</v>
       </c>
       <c r="G50">
-        <v>-1.205218496422167</v>
+        <v>-1.830428263695687</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.80401426132499</v>
       </c>
       <c r="E51">
-        <v>-8.732675125307058</v>
+        <v>-9.409351410851217</v>
       </c>
       <c r="F51">
-        <v>1.126184509234027</v>
+        <v>0.2848209453328781</v>
       </c>
       <c r="G51">
-        <v>-0.6639443007513276</v>
+        <v>-1.044170387573241</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.16382424971885</v>
       </c>
       <c r="E52">
-        <v>-9.587175528184416</v>
+        <v>-8.705699005643366</v>
       </c>
       <c r="F52">
-        <v>0.8877860903710966</v>
+        <v>0.761400023495367</v>
       </c>
       <c r="G52">
-        <v>-0.9739040585022103</v>
+        <v>-1.079533635023736</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.56304490628666</v>
       </c>
       <c r="E53">
-        <v>-8.574943847145892</v>
+        <v>-9.457783440363251</v>
       </c>
       <c r="F53">
-        <v>1.110667358674552</v>
+        <v>0.442080567177142</v>
       </c>
       <c r="G53">
-        <v>-0.7293739227894833</v>
+        <v>-1.02042053387451</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.99102315217092</v>
       </c>
       <c r="E54">
-        <v>-7.344272165399373</v>
+        <v>-9.01182837703589</v>
       </c>
       <c r="F54">
-        <v>0.9290527154097022</v>
+        <v>0.4502065622292618</v>
       </c>
       <c r="G54">
-        <v>-0.9986139704073304</v>
+        <v>-2.870161369577971</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.44632776802825</v>
       </c>
       <c r="E55">
-        <v>-7.901179370388665</v>
+        <v>-7.869244571686574</v>
       </c>
       <c r="F55">
-        <v>1.076836232908934</v>
+        <v>0.212977710184883</v>
       </c>
       <c r="G55">
-        <v>-1.011892568565347</v>
+        <v>-0.7448904497320473</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.91956135331798</v>
       </c>
       <c r="E56">
-        <v>-7.4637831229358</v>
+        <v>-8.572004867514913</v>
       </c>
       <c r="F56">
-        <v>0.9587155272058832</v>
+        <v>0.4797236730812223</v>
       </c>
       <c r="G56">
-        <v>-1.857111260742213</v>
+        <v>-1.515343781450013</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.40381265227639</v>
       </c>
       <c r="E57">
-        <v>-6.505010077557825</v>
+        <v>-7.778693205429198</v>
       </c>
       <c r="F57">
-        <v>1.474750262692673</v>
+        <v>-0.004550632124386904</v>
       </c>
       <c r="G57">
-        <v>-1.43305024043481</v>
+        <v>-1.271267190476166</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.9012001558103</v>
       </c>
       <c r="E58">
-        <v>-6.908723535341637</v>
+        <v>-7.098693019963409</v>
       </c>
       <c r="F58">
-        <v>0.8672533431774242</v>
+        <v>0.3483924844845329</v>
       </c>
       <c r="G58">
-        <v>-1.971225765480891</v>
+        <v>-2.305193599482569</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.40476612397428</v>
       </c>
       <c r="E59">
-        <v>-6.280800800964058</v>
+        <v>-6.805003366669956</v>
       </c>
       <c r="F59">
-        <v>1.319589843039324</v>
+        <v>0.2367340907694324</v>
       </c>
       <c r="G59">
-        <v>-1.35773863996193</v>
+        <v>-2.431461116895911</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.90827097201825</v>
       </c>
       <c r="E60">
-        <v>-6.573956094324606</v>
+        <v>-6.209019959468475</v>
       </c>
       <c r="F60">
-        <v>1.017312646077143</v>
+        <v>0.6850210546055533</v>
       </c>
       <c r="G60">
-        <v>-2.001649678986793</v>
+        <v>-2.587139520880138</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.41237709098305</v>
       </c>
       <c r="E61">
-        <v>-6.423366219673536</v>
+        <v>-6.464652317201467</v>
       </c>
       <c r="F61">
-        <v>0.9041283517125163</v>
+        <v>0.1829656912343477</v>
       </c>
       <c r="G61">
-        <v>-2.261815521281498</v>
+        <v>-1.63999906318573</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.9071704468671</v>
       </c>
       <c r="E62">
-        <v>-5.344543328352219</v>
+        <v>-6.343497523600254</v>
       </c>
       <c r="F62">
-        <v>1.149138742772407</v>
+        <v>0.2981185320518654</v>
       </c>
       <c r="G62">
-        <v>-2.811015162973352</v>
+        <v>-2.684717850650157</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.38332766247118</v>
       </c>
       <c r="E63">
-        <v>-5.384869389390524</v>
+        <v>-6.398921516980131</v>
       </c>
       <c r="F63">
-        <v>0.9775537090700354</v>
+        <v>0.5341208038647364</v>
       </c>
       <c r="G63">
-        <v>-2.355914467689742</v>
+        <v>-3.802685768716497</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.83711076026227</v>
       </c>
       <c r="E64">
-        <v>-4.687955353506086</v>
+        <v>-4.763789179238534</v>
       </c>
       <c r="F64">
-        <v>0.9708261263412485</v>
+        <v>0.2715146482313558</v>
       </c>
       <c r="G64">
-        <v>-2.30904707449028</v>
+        <v>-3.381144073564479</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.25524675299342</v>
       </c>
       <c r="E65">
-        <v>-4.984982492143192</v>
+        <v>-5.219462347786356</v>
       </c>
       <c r="F65">
-        <v>0.8891322403992201</v>
+        <v>0.2599100431359733</v>
       </c>
       <c r="G65">
-        <v>-3.139560323381704</v>
+        <v>-3.75615936170758</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.62695167334778</v>
       </c>
       <c r="E66">
-        <v>-4.628627815531597</v>
+        <v>-5.064878359060521</v>
       </c>
       <c r="F66">
-        <v>0.8693691742804512</v>
+        <v>0.2782572761663393</v>
       </c>
       <c r="G66">
-        <v>-3.068095576825456</v>
+        <v>-3.547591682187956</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.94650268621744</v>
       </c>
       <c r="E67">
-        <v>-4.69416841984461</v>
+        <v>-4.068242742504413</v>
       </c>
       <c r="F67">
-        <v>0.7974451701307688</v>
+        <v>0.03407199588839262</v>
       </c>
       <c r="G67">
-        <v>-3.536951588824738</v>
+        <v>-4.191949644860621</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.19981191097683</v>
       </c>
       <c r="E68">
-        <v>-4.621966430266314</v>
+        <v>-4.200881746189078</v>
       </c>
       <c r="F68">
-        <v>0.3680803245723184</v>
+        <v>-0.3294003894993264</v>
       </c>
       <c r="G68">
-        <v>-3.554457753636404</v>
+        <v>-3.574400479964974</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.37654634371988</v>
       </c>
       <c r="E69">
-        <v>-5.27576939359773</v>
+        <v>-5.556512139703253</v>
       </c>
       <c r="F69">
-        <v>0.3363024735260682</v>
+        <v>0.1341400378613495</v>
       </c>
       <c r="G69">
-        <v>-3.445093881746581</v>
+        <v>-3.114347208554614</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.47495720882141</v>
       </c>
       <c r="E70">
-        <v>-4.861250996831616</v>
+        <v>-3.987821572602195</v>
       </c>
       <c r="F70">
-        <v>0.4664823079222331</v>
+        <v>-0.1566988431265701</v>
       </c>
       <c r="G70">
-        <v>-3.573125919932354</v>
+        <v>-2.794164486178462</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.49117704663832</v>
       </c>
       <c r="E71">
-        <v>-4.816976106458623</v>
+        <v>-5.015006274814048</v>
       </c>
       <c r="F71">
-        <v>-0.02220420196379043</v>
+        <v>-0.2374369625486308</v>
       </c>
       <c r="G71">
-        <v>-3.018165929002168</v>
+        <v>-3.559890358866348</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.42727951599701</v>
       </c>
       <c r="E72">
-        <v>-5.351911155562699</v>
+        <v>-5.303927444977424</v>
       </c>
       <c r="F72">
-        <v>-0.12066003131483</v>
+        <v>-0.4895281027564511</v>
       </c>
       <c r="G72">
-        <v>-3.530959501398657</v>
+        <v>-2.932469147172594</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.29367441161635</v>
       </c>
       <c r="E73">
-        <v>-4.478341348639041</v>
+        <v>-4.108002744291759</v>
       </c>
       <c r="F73">
-        <v>0.1673820250264235</v>
+        <v>-0.003580612251180242</v>
       </c>
       <c r="G73">
-        <v>-2.904653943551638</v>
+        <v>-3.131611703541913</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.09835414726937</v>
       </c>
       <c r="E74">
-        <v>-5.098262269445067</v>
+        <v>-5.149791775178348</v>
       </c>
       <c r="F74">
-        <v>0.2956226115291328</v>
+        <v>-0.171811356824651</v>
       </c>
       <c r="G74">
-        <v>-2.779634501806601</v>
+        <v>-2.368729589472261</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.85266534992475</v>
       </c>
       <c r="E75">
-        <v>-6.265811551998669</v>
+        <v>-7.083060727688931</v>
       </c>
       <c r="F75">
-        <v>0.4347107916996445</v>
+        <v>-0.616529439380329</v>
       </c>
       <c r="G75">
-        <v>-2.814709731795179</v>
+        <v>-2.591009548615546</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.57342494914678</v>
       </c>
       <c r="E76">
-        <v>-6.170156595534648</v>
+        <v>-6.53046462995494</v>
       </c>
       <c r="F76">
-        <v>-0.0614191359889443</v>
+        <v>-0.8484402069606622</v>
       </c>
       <c r="G76">
-        <v>-2.979472272739167</v>
+        <v>-3.915485986876084</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.27307887962429</v>
       </c>
       <c r="E77">
-        <v>-6.819508068916524</v>
+        <v>-6.460110257771773</v>
       </c>
       <c r="F77">
-        <v>-0.3207684004072237</v>
+        <v>-0.5301216527809951</v>
       </c>
       <c r="G77">
-        <v>-2.688508425292622</v>
+        <v>-3.453750958331775</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.96346011501795</v>
       </c>
       <c r="E78">
-        <v>-6.18634589011207</v>
+        <v>-7.96111825235419</v>
       </c>
       <c r="F78">
-        <v>0.06102983798100289</v>
+        <v>-0.7399785236358762</v>
       </c>
       <c r="G78">
-        <v>-2.705031358079125</v>
+        <v>-2.615212947053158</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.65939396894317</v>
       </c>
       <c r="E79">
-        <v>-7.035217399797894</v>
+        <v>-8.192247037231677</v>
       </c>
       <c r="F79">
-        <v>-0.3934731715732178</v>
+        <v>-0.8841884087369192</v>
       </c>
       <c r="G79">
-        <v>-3.183011233584638</v>
+        <v>-2.580991837813712</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.3705064828839</v>
       </c>
       <c r="E80">
-        <v>-8.772181532549974</v>
+        <v>-8.85163360901455</v>
       </c>
       <c r="F80">
-        <v>-0.2633273868542349</v>
+        <v>-0.6436844528594116</v>
       </c>
       <c r="G80">
-        <v>-1.874518109187701</v>
+        <v>-2.072545011710285</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.10267286941552</v>
       </c>
       <c r="E81">
-        <v>-9.631812696478022</v>
+        <v>-9.539649193473915</v>
       </c>
       <c r="F81">
-        <v>-0.1524394660669957</v>
+        <v>-1.228108360892623</v>
       </c>
       <c r="G81">
-        <v>-2.524682768736248</v>
+        <v>-1.619728592848773</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.86269414490167</v>
       </c>
       <c r="E82">
-        <v>-9.959099098434383</v>
+        <v>-9.42538220883837</v>
       </c>
       <c r="F82">
-        <v>-0.4806522229533708</v>
+        <v>-0.8601913048532229</v>
       </c>
       <c r="G82">
-        <v>-1.847980776144903</v>
+        <v>-2.214487962252077</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.65062226429394</v>
       </c>
       <c r="E83">
-        <v>-10.93161153395163</v>
+        <v>-11.72935657209086</v>
       </c>
       <c r="F83">
-        <v>-0.4411910226583661</v>
+        <v>-1.121024501714269</v>
       </c>
       <c r="G83">
-        <v>-2.300389997905086</v>
+        <v>-1.388993500398189</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-15.45916153849526</v>
       </c>
       <c r="E84">
-        <v>-11.87518702055986</v>
+        <v>-11.0773604698885</v>
       </c>
       <c r="F84">
-        <v>-0.4359038204596715</v>
+        <v>-1.266285175690206</v>
       </c>
       <c r="G84">
-        <v>-1.278798681578008</v>
+        <v>-1.281973494750169</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-15.28267221590758</v>
       </c>
       <c r="E85">
-        <v>-12.99990146747491</v>
+        <v>-12.83226188818496</v>
       </c>
       <c r="F85">
-        <v>-0.8703895790956953</v>
+        <v>-1.482221893554459</v>
       </c>
       <c r="G85">
-        <v>-2.015421548430161</v>
+        <v>-0.8491958080378647</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-15.11509414998545</v>
       </c>
       <c r="E86">
-        <v>-13.919186219506</v>
+        <v>-13.33380396995648</v>
       </c>
       <c r="F86">
-        <v>-0.2696994276050055</v>
+        <v>-1.406325954968855</v>
       </c>
       <c r="G86">
-        <v>-1.666321210768475</v>
+        <v>-1.72353405877816</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.94730375949068</v>
       </c>
       <c r="E87">
-        <v>-15.3838713240729</v>
+        <v>-16.5565558961512</v>
       </c>
       <c r="F87">
-        <v>-1.115652571249099</v>
+        <v>-1.534683735709306</v>
       </c>
       <c r="G87">
-        <v>-1.330830525818733</v>
+        <v>-1.162098640773159</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.77722017132195</v>
       </c>
       <c r="E88">
-        <v>-16.76156897142645</v>
+        <v>-16.65001001424749</v>
       </c>
       <c r="F88">
-        <v>-1.028635849725278</v>
+        <v>-1.531026958750557</v>
       </c>
       <c r="G88">
-        <v>-1.235016716821147</v>
+        <v>-1.166538082341322</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.60882962018501</v>
       </c>
       <c r="E89">
-        <v>-17.984583003626</v>
+        <v>-18.83132613052821</v>
       </c>
       <c r="F89">
-        <v>-1.135149574774073</v>
+        <v>-1.345445132167531</v>
       </c>
       <c r="G89">
-        <v>-0.9187205749080989</v>
+        <v>-0.7863782064301938</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.44411954722509</v>
       </c>
       <c r="E90">
-        <v>-19.99781575016402</v>
+        <v>-20.15107742447962</v>
       </c>
       <c r="F90">
-        <v>-1.131390648783778</v>
+        <v>-1.688148798180177</v>
       </c>
       <c r="G90">
-        <v>-0.6688372870583704</v>
+        <v>-0.3169097435061468</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.29341564298671</v>
       </c>
       <c r="E91">
-        <v>-21.83591882140341</v>
+        <v>-21.3524408224485</v>
       </c>
       <c r="F91">
-        <v>-1.051107844812406</v>
+        <v>-1.949750884263169</v>
       </c>
       <c r="G91">
-        <v>-1.031246017787927</v>
+        <v>-0.8208045694930749</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.17370045255251</v>
       </c>
       <c r="E92">
-        <v>-23.72969495209311</v>
+        <v>-23.86738773277033</v>
       </c>
       <c r="F92">
-        <v>-1.627456436382791</v>
+        <v>-2.170013494835445</v>
       </c>
       <c r="G92">
-        <v>-1.065973640494881</v>
+        <v>-0.261146914442663</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.09224023751532</v>
       </c>
       <c r="E93">
-        <v>-26.33391167052814</v>
+        <v>-25.93530180295097</v>
       </c>
       <c r="F93">
-        <v>-1.214536001197307</v>
+        <v>-2.286204454880534</v>
       </c>
       <c r="G93">
-        <v>-0.3769597290429869</v>
+        <v>-0.3795518862002362</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.05603328112506</v>
       </c>
       <c r="E94">
-        <v>-28.13502616607288</v>
+        <v>-28.16270872768177</v>
       </c>
       <c r="F94">
-        <v>-2.010222319085352</v>
+        <v>-2.228015932135457</v>
       </c>
       <c r="G94">
-        <v>-0.69822831035602</v>
+        <v>-0.7415302460096871</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.0736526874517</v>
       </c>
       <c r="E95">
-        <v>-30.77041237110272</v>
+        <v>-30.22032278373197</v>
       </c>
       <c r="F95">
-        <v>-1.88266668539107</v>
+        <v>-2.539465953759864</v>
       </c>
       <c r="G95">
-        <v>-0.3362797454564225</v>
+        <v>-0.1874177547375543</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.1368855301035</v>
       </c>
       <c r="E96">
-        <v>-32.64199671491782</v>
+        <v>-32.40976071814546</v>
       </c>
       <c r="F96">
-        <v>-1.912886169816528</v>
+        <v>-2.543695240407045</v>
       </c>
       <c r="G96">
-        <v>-0.4737799438845121</v>
+        <v>-0.6913324439977181</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-14.23531477487514</v>
       </c>
       <c r="E97">
-        <v>-34.65387318349055</v>
+        <v>-35.97270746145539</v>
       </c>
       <c r="F97">
-        <v>-2.138914261773961</v>
+        <v>-2.732324909024333</v>
       </c>
       <c r="G97">
-        <v>-1.410492183130216</v>
+        <v>-1.666321210768475</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-14.36034177575754</v>
       </c>
       <c r="E98">
-        <v>-37.97387635323699</v>
+        <v>-36.40866365417382</v>
       </c>
       <c r="F98">
-        <v>-2.511097029696597</v>
+        <v>-2.612000476539948</v>
       </c>
       <c r="G98">
-        <v>-0.9127251769364787</v>
+        <v>-0.8222645200758936</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-14.48813723775508</v>
       </c>
       <c r="E99">
-        <v>-40.81414204355885</v>
+        <v>-39.73425496084572</v>
       </c>
       <c r="F99">
-        <v>-2.30314535705799</v>
+        <v>-2.92890398948417</v>
       </c>
       <c r="G99">
-        <v>-1.878398068559727</v>
+        <v>-2.356232280061512</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.59871526217086</v>
       </c>
       <c r="E100">
-        <v>-43.28912517076299</v>
+        <v>-43.33774966042035</v>
       </c>
       <c r="F100">
-        <v>-2.371614506753141</v>
+        <v>-3.093217437475801</v>
       </c>
       <c r="G100">
-        <v>-1.75801339056967</v>
+        <v>-1.779475657300765</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.6760590853037</v>
       </c>
       <c r="E101">
-        <v>-45.51168889254258</v>
+        <v>-45.14230806044792</v>
       </c>
       <c r="F101">
-        <v>-2.887580351032609</v>
+        <v>-3.278143609809835</v>
       </c>
       <c r="G101">
-        <v>-2.14156988620409</v>
+        <v>-2.393419638104145</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.70084413413521</v>
       </c>
       <c r="E102">
-        <v>-47.56015995957129</v>
+        <v>-47.49476653066353</v>
       </c>
       <c r="F102">
-        <v>-2.745846590130355</v>
+        <v>-3.250839727974701</v>
       </c>
       <c r="G102">
-        <v>-2.532217570383629</v>
+        <v>-2.616298805990039</v>
       </c>
     </row>
   </sheetData>
